--- a/measurements/27/Filled_2D_sections/coronal/week27_coronal_Batch_Allmarks.xlsx
+++ b/measurements/27/Filled_2D_sections/coronal/week27_coronal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AE27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,92 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +586,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.772159428911363</v>
+        <v>1819.047619047619</v>
       </c>
       <c r="D2" t="n">
-        <v>11.9613732361212</v>
+        <v>233.5315727052234</v>
       </c>
       <c r="E2" t="n">
-        <v>10.53735432101459</v>
+        <v>205.7292986483801</v>
       </c>
       <c r="F2" t="n">
         <v>1.13514008087084</v>
@@ -525,24 +605,48 @@
         <v>0.4191434888818512</v>
       </c>
       <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18.09523809523809</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.032738095238093</v>
+      </c>
+      <c r="L2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.7485708841463415</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.926829268292683</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.8377000762195123</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>18.09523809523809</v>
+      </c>
+      <c r="N2" t="n">
+        <v>14.61495535714286</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.468377976190476</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>5.160291493158835</v>
+      <c r="AE2" s="2" t="n">
+        <v>1966.995464852608</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +657,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.797144556811422</v>
+        <v>1828.571428571428</v>
       </c>
       <c r="D3" t="n">
-        <v>12.2087423394366</v>
+        <v>238.3611599604289</v>
       </c>
       <c r="E3" t="n">
-        <v>10.53143622526308</v>
+        <v>205.613754874184</v>
       </c>
       <c r="F3" t="n">
         <v>1.159266606975215</v>
@@ -572,24 +676,48 @@
         <v>0.404436937592752</v>
       </c>
       <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.428571428571428</v>
+      </c>
+      <c r="J3" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.307570684523808</v>
+      </c>
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.7560975609756098</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.951219512195122</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.8536585365853659</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="N3" t="n">
+        <v>14.76190476190476</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.468377976190476</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.428571428571428</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>12.58450802811762</v>
+      <c r="AE3" s="2" t="n">
+        <v>245.6975376918202</v>
       </c>
     </row>
     <row r="4">
@@ -600,43 +728,67 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.851873884592504</v>
+        <v>1849.433106575964</v>
       </c>
       <c r="D4" t="n">
-        <v>12.33834500719861</v>
+        <v>240.8914977595919</v>
       </c>
       <c r="E4" t="n">
-        <v>10.62307912838168</v>
+        <v>207.4029734588805</v>
       </c>
       <c r="F4" t="n">
         <v>1.161465979692673</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4005027918886813</v>
+        <v>0.4005027918886814</v>
       </c>
       <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.552641369047619</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.7722942073170732</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.951219512195122</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.8617568597560976</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="N4" t="n">
+        <v>15.078125</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.65625</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>10.1310844502798</v>
+      <c r="AE4" s="2" t="n">
+        <v>197.7973630768912</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +799,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.894110648423558</v>
+        <v>1865.532879818594</v>
       </c>
       <c r="D5" t="n">
-        <v>12.56550860404968</v>
+        <v>245.3265965552557</v>
       </c>
       <c r="E5" t="n">
-        <v>10.72900950908661</v>
+        <v>209.4711380345481</v>
       </c>
       <c r="F5" t="n">
         <v>1.171171354951984</v>
@@ -666,23 +818,47 @@
         <v>0.3895143877607729</v>
       </c>
       <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.646949404761905</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9.689825148809522</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.7465701219512195</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.951219512195122</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.8488948170731707</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="N5" t="n">
+        <v>14.57589285714286</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.965029761904762</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.646949404761905</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AE5" s="2" t="n">
         <v>1.242689382299725</v>
       </c>
     </row>
@@ -694,17 +870,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.252528256989887</v>
+        <v>2002.154195011338</v>
       </c>
       <c r="D6" t="n">
-        <v>12.95820386526061</v>
+        <v>252.9935040360405</v>
       </c>
       <c r="E6" t="n">
-        <v>9.898725841103531</v>
+        <v>193.2608378501165</v>
       </c>
       <c r="F6" t="n">
         <v>1.309077963494341</v>
@@ -713,23 +889,53 @@
         <v>0.3930869672276988</v>
       </c>
       <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.980282738095238</v>
+      </c>
+      <c r="J6" t="n">
+        <v>14.63541666666667</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.149863591269842</v>
+      </c>
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.7462842987804879</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.7496189024390244</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.7479516006097562</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>14.63541666666667</v>
+      </c>
+      <c r="N6" t="n">
+        <v>14.5703125</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.465401785714286</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.248883928571428</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.9988839285714285</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.980282738095238</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AE6" s="2" t="n">
         <v>0.4125364135276864</v>
       </c>
     </row>
@@ -741,17 +947,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.271267102914932</v>
+        <v>2009.297052154195</v>
       </c>
       <c r="D7" t="n">
-        <v>12.86309424842276</v>
+        <v>251.1366019930158</v>
       </c>
       <c r="E7" t="n">
-        <v>9.913013347765295</v>
+        <v>193.539784408751</v>
       </c>
       <c r="F7" t="n">
         <v>1.297596784868903</v>
@@ -760,24 +966,54 @@
         <v>0.4003446080192343</v>
       </c>
       <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8798363095238094</v>
+      </c>
+      <c r="J7" t="n">
+        <v>14.59449404761905</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.213913690476191</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.653391768292683</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.7475228658536586</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.7004573170731707</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>14.59449404761905</v>
+      </c>
+      <c r="N7" t="n">
+        <v>12.75669642857143</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.898809523809524</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.8798363095238094</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.311848958333333</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>1.6</v>
+      <c r="AE7" s="2" t="n">
+        <v>5.6</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1024,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.304878048780488</v>
+        <v>2022.108843537415</v>
       </c>
       <c r="D8" t="n">
-        <v>12.92616219636871</v>
+        <v>252.36792859577</v>
       </c>
       <c r="E8" t="n">
-        <v>9.947506340538583</v>
+        <v>194.2132190295628</v>
       </c>
       <c r="F8" t="n">
         <v>1.299437442295599</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3989753518259638</v>
+        <v>0.3989753518259637</v>
       </c>
       <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.160714285714286</v>
+      </c>
+      <c r="J8" t="n">
+        <v>15.03720238095238</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.062437996031746</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.6052782012195123</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.7701981707317074</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.6877381859756098</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>15.03720238095238</v>
+      </c>
+      <c r="N8" t="n">
+        <v>11.81733630952381</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.185267857142857</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.269345238095238</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.160714285714286</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6411775914634147</v>
+      <c r="AE8" s="2" t="n">
+        <v>1.457868303571428</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1101,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.414931588340274</v>
+        <v>2064.0589569161</v>
       </c>
       <c r="D9" t="n">
-        <v>11.82931919795711</v>
+        <v>230.9533748172578</v>
       </c>
       <c r="E9" t="n">
-        <v>9.984450686268691</v>
+        <v>194.9345133985792</v>
       </c>
       <c r="F9" t="n">
         <v>1.184774162310763</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4862765609388848</v>
+        <v>0.486276560938885</v>
       </c>
       <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.145833333333333</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11.36160714285714</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.429253472222222</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.5819359756097561</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.5819359756097561</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.5819359756097561</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>11.36160714285714</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.389880952380953</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.103422619047619</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.2890625</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.145833333333333</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.7264529344512195</v>
+      <c r="AE9" s="2" t="n">
+        <v>14.18312872023809</v>
       </c>
     </row>
     <row r="10">
@@ -882,17 +1178,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.356930398572278</v>
+        <v>2041.950113378685</v>
       </c>
       <c r="D10" t="n">
-        <v>13.23313256298623</v>
+        <v>258.3611595630646</v>
       </c>
       <c r="E10" t="n">
-        <v>10.0105743001147</v>
+        <v>195.4445458593823</v>
       </c>
       <c r="F10" t="n">
         <v>1.321915423257446</v>
@@ -901,24 +1197,57 @@
         <v>0.3844151911586486</v>
       </c>
       <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9356398809523809</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14.57589285714286</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.680803571428571</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.6009908536585367</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.7465701219512195</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.6737804878048781</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>14.57589285714286</v>
+      </c>
+      <c r="N10" t="n">
+        <v>11.73363095238095</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.258556547619047</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4.397321428571428</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.551339285714286</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.313244047619047</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.9356398809523809</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.6838152629573171</v>
+      <c r="AE10" s="2" t="n">
+        <v>7.096968005952381</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1258,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.364961332540155</v>
+        <v>2045.01133786848</v>
       </c>
       <c r="D11" t="n">
-        <v>13.81258037322905</v>
+        <v>269.6741882392338</v>
       </c>
       <c r="E11" t="n">
-        <v>10.08792972855452</v>
+        <v>196.9548185098739</v>
       </c>
       <c r="F11" t="n">
         <v>1.369218535903524</v>
@@ -948,16 +1277,57 @@
         <v>0.3533676789814297</v>
       </c>
       <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.233258928571429</v>
+      </c>
+      <c r="J11" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.623883928571429</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.5773628048780488</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.7317073170731707</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.6545350609756098</v>
+      <c r="M11" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="N11" t="n">
+        <v>11.27232142857143</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8.14360119047619</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7.1875</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.615327380952381</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.629464285714286</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.233258928571429</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1338,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.376859012492564</v>
+        <v>2049.546485260771</v>
       </c>
       <c r="D12" t="n">
-        <v>13.92688017938195</v>
+        <v>271.9057558831714</v>
       </c>
       <c r="E12" t="n">
-        <v>10.09038107860379</v>
+        <v>197.0026782013121</v>
       </c>
       <c r="F12" t="n">
         <v>1.380213499459727</v>
@@ -987,16 +1357,54 @@
         <v>0.3483620476725123</v>
       </c>
       <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.235863095238095</v>
+      </c>
+      <c r="J12" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8.006572420634919</v>
+      </c>
+      <c r="L12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.577172256097561</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.7317073170731707</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.6544397865853658</v>
+      <c r="M12" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="N12" t="n">
+        <v>11.26860119047619</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>8.405877976190476</v>
+      </c>
+      <c r="R12" t="n">
+        <v>8.346354166666666</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.497023809523809</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.235863095238095</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="n">
+        <v>14.18312872023809</v>
       </c>
     </row>
     <row r="13">
@@ -1007,35 +1415,73 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.414336704342653</v>
+        <v>2063.832199546485</v>
       </c>
       <c r="D13" t="n">
-        <v>13.43560858761392</v>
+        <v>262.3142629010337</v>
       </c>
       <c r="E13" t="n">
-        <v>10.15936711648615</v>
+        <v>198.3495484647297</v>
       </c>
       <c r="F13" t="n">
         <v>1.322484799846561</v>
       </c>
       <c r="G13" t="n">
-        <v>0.376912410366225</v>
+        <v>0.3769124103662251</v>
       </c>
       <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.71391369047619</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13.80952380952381</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.705853174603174</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>13.80952380952381</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8.878348214285714</v>
+      </c>
+      <c r="O13" t="n">
+        <v>8.852306547619047</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>8.444940476190476</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.536086309523809</v>
+      </c>
+      <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.7073170731707318</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.7073170731707318</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.7073170731707318</v>
+      <c r="U13" t="n">
+        <v>2.71391369047619</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="n">
+        <v>11.82803199404762</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1492,73 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.399464604402142</v>
+        <v>2058.163265306122</v>
       </c>
       <c r="D14" t="n">
-        <v>13.23211724002187</v>
+        <v>258.3413365909032</v>
       </c>
       <c r="E14" t="n">
-        <v>10.19140878247052</v>
+        <v>198.9751238482339</v>
       </c>
       <c r="F14" t="n">
         <v>1.298359973822407</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3875269249450499</v>
+        <v>0.38752692494505</v>
       </c>
       <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.477678571428571</v>
+      </c>
+      <c r="J14" t="n">
+        <v>14.09784226190476</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7.650669642857142</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>14.09784226190476</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8.939732142857142</v>
+      </c>
+      <c r="O14" t="n">
+        <v>8.731398809523808</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8.418898809523808</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3.238467261904762</v>
+      </c>
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.7220846036585367</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.7220846036585367</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.7220846036585367</v>
+      <c r="U14" t="n">
+        <v>2.477678571428571</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="n">
+        <v>8.717137896825397</v>
       </c>
     </row>
     <row r="15">
@@ -1085,17 +1569,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.370612730517549</v>
+        <v>2047.165532879819</v>
       </c>
       <c r="D15" t="n">
-        <v>12.99413285313583</v>
+        <v>253.6949747516995</v>
       </c>
       <c r="E15" t="n">
-        <v>10.16283383311295</v>
+        <v>198.4172319798242</v>
       </c>
       <c r="F15" t="n">
         <v>1.278593457938654</v>
@@ -1104,16 +1588,54 @@
         <v>0.3997045532361143</v>
       </c>
       <c r="H15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.925223214285714</v>
+      </c>
+      <c r="J15" t="n">
+        <v>14.06994047619048</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7.437996031746032</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>14.06994047619048</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9.110863095238095</v>
+      </c>
+      <c r="O15" t="n">
+        <v>8.898809523809524</v>
+      </c>
+      <c r="P15" t="n">
         <v>1</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.7206554878048781</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.7206554878048781</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.7206554878048781</v>
+      <c r="Q15" t="n">
+        <v>8.095238095238095</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.527901785714286</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.925223214285714</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1646,73 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.30755502676978</v>
+        <v>2023.12925170068</v>
       </c>
       <c r="D16" t="n">
-        <v>12.73002487566413</v>
+        <v>248.5385809058235</v>
       </c>
       <c r="E16" t="n">
-        <v>10.18895741206844</v>
+        <v>198.9272637594314</v>
       </c>
       <c r="F16" t="n">
         <v>1.249394257020438</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4115720413488678</v>
+        <v>0.4115720413488677</v>
       </c>
       <c r="H16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.54203869047619</v>
+      </c>
+      <c r="J16" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7.185329861111111</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="N16" t="n">
+        <v>9.339657738095237</v>
+      </c>
+      <c r="O16" t="n">
+        <v>8.876488095238095</v>
+      </c>
+      <c r="P16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.6829268292682927</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.6829268292682927</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.6829268292682927</v>
+      <c r="Q16" t="n">
+        <v>8.095238095238095</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.925223214285714</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.54203869047619</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="n">
+        <v>6.539084383753501</v>
       </c>
     </row>
     <row r="17">
@@ -1163,35 +1723,73 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.229030339083879</v>
+        <v>1993.197278911565</v>
       </c>
       <c r="D17" t="n">
-        <v>12.5634778679871</v>
+        <v>245.2869488511766</v>
       </c>
       <c r="E17" t="n">
-        <v>10.13180751916839</v>
+        <v>197.8114801361447</v>
       </c>
       <c r="F17" t="n">
         <v>1.240003606880433</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4163046554946713</v>
+        <v>0.4163046554946714</v>
       </c>
       <c r="H17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.084449404761905</v>
+      </c>
+      <c r="J17" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.998387896825396</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="N17" t="n">
+        <v>9.858630952380953</v>
+      </c>
+      <c r="O17" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7.935267857142857</v>
+      </c>
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.504954268292683</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.6585365853658537</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.5817454268292683</v>
+      <c r="U17" t="n">
+        <v>1.683407738095238</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.084449404761905</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="n">
+        <v>5.667162698412699</v>
       </c>
     </row>
     <row r="18">
@@ -1202,17 +1800,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.141879833432481</v>
+        <v>1959.977324263038</v>
       </c>
       <c r="D18" t="n">
-        <v>12.33386291236412</v>
+        <v>240.8039901937757</v>
       </c>
       <c r="E18" t="n">
-        <v>10.04853402696005</v>
+        <v>196.1856643358866</v>
       </c>
       <c r="F18" t="n">
         <v>1.227429083612851</v>
@@ -1221,16 +1819,51 @@
         <v>0.424750161644762</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5465891768292683</v>
+        <v>1.395089285714286</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6247141768292683</v>
+        <v>12.19680059523809</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5856516768292683</v>
+        <v>8.024925595238095</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>12.19680059523809</v>
+      </c>
+      <c r="N18" t="n">
+        <v>10.67150297619048</v>
+      </c>
+      <c r="O18" t="n">
+        <v>8.372395833333332</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7.488839285714286</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.395089285714286</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="n">
+        <v>4.573660714285714</v>
       </c>
     </row>
     <row r="19">
@@ -1241,17 +1874,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.056216537775134</v>
+        <v>1927.324263038549</v>
       </c>
       <c r="D19" t="n">
-        <v>11.44397799561663</v>
+        <v>223.4300465810867</v>
       </c>
       <c r="E19" t="n">
-        <v>9.922398101992723</v>
+        <v>193.7230105627151</v>
       </c>
       <c r="F19" t="n">
         <v>1.153347998939725</v>
@@ -1260,16 +1893,54 @@
         <v>0.4851561049204565</v>
       </c>
       <c r="H19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.824032738095238</v>
+      </c>
+      <c r="J19" t="n">
+        <v>10.66034226190476</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.459759424603174</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.5460175304878049</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.5460175304878049</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.5460175304878049</v>
+      <c r="M19" t="n">
+        <v>10.66034226190476</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7.821800595238095</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7.040550595238095</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.500372023809524</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.9114583333333333</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.824032738095238</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +1951,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.907198096371208</v>
+        <v>1870.521541950113</v>
       </c>
       <c r="D20" t="n">
-        <v>11.3119240010657</v>
+        <v>220.851849544616</v>
       </c>
       <c r="E20" t="n">
-        <v>9.804631582120571</v>
+        <v>191.4237594604492</v>
       </c>
       <c r="F20" t="n">
         <v>1.153732693199179</v>
@@ -1299,16 +1970,51 @@
         <v>0.4819150583397522</v>
       </c>
       <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8500744047619048</v>
+      </c>
+      <c r="J20" t="n">
+        <v>10.17671130952381</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.991815476190476</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.5212461890243902</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.5212461890243902</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.5212461890243902</v>
+      <c r="M20" t="n">
+        <v>10.17671130952381</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7.358630952380952</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6.568080357142857</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5.005580357142857</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.8500744047619048</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="n">
+        <v>1.988173558897243</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +2025,70 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.721891731112433</v>
+        <v>1799.886621315193</v>
       </c>
       <c r="D21" t="n">
-        <v>11.02169241847062</v>
+        <v>215.1854234082358</v>
       </c>
       <c r="E21" t="n">
-        <v>9.658290124521024</v>
+        <v>188.566616716839</v>
       </c>
       <c r="F21" t="n">
         <v>1.141163940653233</v>
       </c>
       <c r="G21" t="n">
-        <v>0.488460348309399</v>
+        <v>0.4884603483093991</v>
       </c>
       <c r="H21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8407738095238094</v>
+      </c>
+      <c r="J21" t="n">
+        <v>9.875372023809524</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.735119047619047</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.5058117378048781</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.5058117378048781</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.5058117378048781</v>
+      <c r="M21" t="n">
+        <v>9.875372023809524</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.793154761904762</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6.40438988095238</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.8407738095238094</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="n">
+        <v>1.387803819444444</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2098,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="n">
+        <v>1.077473958333333</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2120,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="n">
+        <v>0.8798363095238094</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2137,62 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="n">
+        <v>1.904761904761905</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="n">
+        <v>1.311848958333333</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/27/Filled_2D_sections/coronal/week27_coronal_Batch_Allmarks.xlsx
+++ b/measurements/27/Filled_2D_sections/coronal/week27_coronal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2198,4 +2404,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week27_coronal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coronal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1966.995464852608</v>
+      </c>
+      <c r="D10" t="n">
+        <v>93.46499382605937</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1799.886621315193</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2064.0589569161</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>245.6975376918202</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15.50577340899009</v>
+      </c>
+      <c r="E11" t="n">
+        <v>215.1854234082358</v>
+      </c>
+      <c r="F11" t="n">
+        <v>271.9057558831714</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.242689382299725</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.08035369177423603</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.13514008087084</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.380213499459727</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4125364135276864</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.04193827976990897</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3483620476725123</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4884603483093991</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis1_s00_idx0099.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis1_s01_idx0100.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis1_s02_idx0102.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis1_s03_idx0104.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis1_s04_idx0106.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis1_s05_idx0108.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis1_s06_idx0110.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis1_s07_idx0112.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis1_s08_idx0114.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis1_s09_idx0116.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis1_s10_idx0118.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis1_s11_idx0120.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis1_s12_idx0122.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis1_s13_idx0124.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis1_s14_idx0126.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis1_s15_idx0128.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis1_s16_idx0130.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis1_s17_idx0132.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis1_s18_idx0134.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis1_s19_idx0136.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.99472291830968</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.7181848464596079</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.050062654772261</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.8870412083230169</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>42</v>
+      </c>
+      <c r="C48" t="n">
+        <v>12.50509318310658</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.984571528687184</v>
+      </c>
+      <c r="E48" t="n">
+        <v>8.372395833333332</v>
+      </c>
+      <c r="F48" t="n">
+        <v>18.57142857142857</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>31</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5.968942012288786</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.910722842317517</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.965029761904762</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8.444940476190476</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>39</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.640672695360195</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.6282168438359236</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.824032738095238</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.71391369047619</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>